--- a/Excel/ExclusiveAttrConfig.xlsx
+++ b/Excel/ExclusiveAttrConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -60,11 +60,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="45">
   <si>
     <t>ID</t>
   </si>
   <si>
+    <t>Cycle</t>
+  </si>
+  <si>
     <t>Level</t>
   </si>
   <si>
@@ -110,6 +113,9 @@
     <t>200,120,300,4</t>
   </si>
   <si>
+    <t>#</t>
+  </si>
+  <si>
     <t>14,16,15,2003,2002</t>
   </si>
   <si>
@@ -128,6 +134,33 @@
     <t>10,20,30,0,0,0</t>
   </si>
   <si>
+    <t>2001,2002,2003</t>
+  </si>
+  <si>
+    <t>5,10,20</t>
+  </si>
+  <si>
+    <t>0,0,0</t>
+  </si>
+  <si>
+    <t>10,20,40</t>
+  </si>
+  <si>
+    <t>2001,2002,2003,2010</t>
+  </si>
+  <si>
+    <t>20,40,80,20</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>40,80,160,40</t>
+  </si>
+  <si>
+    <t>2001,2002,2003,2012</t>
+  </si>
+  <si>
     <t>Name</t>
   </si>
   <si>
@@ -153,9 +186,6 @@
   </si>
   <si>
     <t>SuitId</t>
-  </si>
-  <si>
-    <t>#</t>
   </si>
   <si>
     <t>string</t>
@@ -1154,34 +1184,34 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="6"/>
+  <dimension ref="A1:U32"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="5" customWidth="1"/>
     <col min="2" max="2" width="9" style="5"/>
-    <col min="3" max="3" width="9.875" style="4" customWidth="1"/>
-    <col min="4" max="4" width="12.125" style="4" customWidth="1"/>
-    <col min="5" max="5" width="19.25" style="5" customWidth="1"/>
-    <col min="6" max="7" width="21.25" style="5" customWidth="1"/>
-    <col min="8" max="16367" width="9" style="5"/>
-    <col min="16368" max="16384" width="9" style="4"/>
+    <col min="3" max="4" width="9.875" style="4" customWidth="1"/>
+    <col min="5" max="5" width="12.125" style="4" customWidth="1"/>
+    <col min="6" max="6" width="19.25" style="5" customWidth="1"/>
+    <col min="7" max="8" width="21.25" style="5" customWidth="1"/>
+    <col min="9" max="16368" width="9" style="5"/>
+    <col min="16369" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="4" customFormat="1" customHeight="1" spans="1:7">
+    <row r="1" s="4" customFormat="1" customHeight="1" spans="1:8">
       <c r="A1" s="5"/>
       <c r="B1" s="5"/>
-      <c r="E1" s="5"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
-    </row>
-    <row r="2" s="4" customFormat="1" customHeight="1" spans="1:7">
+      <c r="H1" s="5"/>
+    </row>
+    <row r="2" s="4" customFormat="1" customHeight="1" spans="1:8">
       <c r="A2" s="5"/>
       <c r="B2" s="5"/>
-      <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
-    </row>
-    <row r="3" s="4" customFormat="1" customHeight="1" spans="1:7">
+      <c r="H2" s="5"/>
+    </row>
+    <row r="3" s="4" customFormat="1" customHeight="1" spans="1:8">
       <c r="A3" s="5"/>
       <c r="B3" s="5"/>
       <c r="C3" s="6" t="s">
@@ -1199,12 +1229,15 @@
       <c r="G3" s="6" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" s="4" customFormat="1" customHeight="1" spans="1:7">
+      <c r="H3" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" s="4" customFormat="1" customHeight="1" spans="1:8">
       <c r="A4" s="5"/>
       <c r="B4" s="5"/>
       <c r="C4" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>1</v>
@@ -1218,35 +1251,41 @@
       <c r="G4" s="6" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" s="4" customFormat="1" customHeight="1" spans="1:7">
+      <c r="H4" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" s="4" customFormat="1" customHeight="1" spans="1:8">
       <c r="A5" s="5"/>
       <c r="B5" s="5"/>
       <c r="C5" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" s="4" customFormat="1" customHeight="1" spans="3:7">
+        <v>8</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" s="4" customFormat="1" customHeight="1" spans="3:8">
       <c r="C6" s="4">
         <v>1</v>
       </c>
       <c r="D6" s="4">
         <v>1</v>
       </c>
-      <c r="E6" s="7" t="s">
-        <v>8</v>
+      <c r="E6" s="4">
+        <v>1</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>9</v>
@@ -1254,33 +1293,39 @@
       <c r="G6" s="7" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" s="4" customFormat="1" customHeight="1" spans="3:7">
+      <c r="H6" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" s="4" customFormat="1" customHeight="1" spans="3:8">
       <c r="C7" s="4">
         <v>2</v>
       </c>
       <c r="D7" s="4">
+        <v>1</v>
+      </c>
+      <c r="E7" s="4">
         <v>2</v>
       </c>
-      <c r="E7" s="7" t="s">
-        <v>8</v>
-      </c>
       <c r="F7" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H7" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" s="4" customFormat="1" customHeight="1" spans="3:7">
+    </row>
+    <row r="8" s="4" customFormat="1" customHeight="1" spans="3:8">
       <c r="C8" s="4">
         <v>3</v>
       </c>
       <c r="D8" s="4">
+        <v>1</v>
+      </c>
+      <c r="E8" s="4">
         <v>3</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>12</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>13</v>
@@ -1288,61 +1333,371 @@
       <c r="G8" s="7" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="9" s="4" customFormat="1" customHeight="1" spans="3:7">
+      <c r="H8" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" s="4" customFormat="1" customHeight="1" spans="3:8">
       <c r="C9" s="4">
         <v>4</v>
       </c>
       <c r="D9" s="4">
+        <v>1</v>
+      </c>
+      <c r="E9" s="4">
         <v>4</v>
       </c>
-      <c r="E9" s="7" t="s">
-        <v>12</v>
-      </c>
       <c r="F9" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="G9" s="7" t="s">
+    </row>
+    <row r="10" s="4" customFormat="1" customHeight="1" spans="14:21">
+      <c r="N10" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="O10" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="P10" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q10" s="4">
+        <v>1</v>
+      </c>
+      <c r="R10" s="4">
+        <v>5</v>
+      </c>
+      <c r="S10" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="T10" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="U10" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" s="4" customFormat="1" customHeight="1" spans="14:21">
+      <c r="N11" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="O11" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="P11" s="4">
+        <v>6</v>
+      </c>
+      <c r="Q11" s="4">
+        <v>1</v>
+      </c>
+      <c r="R11" s="4">
+        <v>6</v>
+      </c>
+      <c r="S11" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="T11" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U11" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="3:8">
+      <c r="C13" s="4">
+        <v>7</v>
+      </c>
+      <c r="D13" s="4">
+        <v>2</v>
+      </c>
+      <c r="E13" s="4">
+        <v>1</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="3:8">
+      <c r="C14" s="4">
+        <v>8</v>
+      </c>
+      <c r="D14" s="4">
+        <v>2</v>
+      </c>
+      <c r="E14" s="4">
+        <v>2</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="3:8">
+      <c r="C15" s="4">
+        <v>9</v>
+      </c>
+      <c r="D15" s="4">
+        <v>2</v>
+      </c>
+      <c r="E15" s="4">
+        <v>3</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="3:8">
+      <c r="C16" s="4">
+        <v>10</v>
+      </c>
+      <c r="D16" s="4">
+        <v>2</v>
+      </c>
+      <c r="E16" s="4">
+        <v>4</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="14:21">
+      <c r="N17" s="4"/>
+      <c r="O17" s="4"/>
+      <c r="P17" s="4"/>
+      <c r="Q17" s="4"/>
+      <c r="R17" s="4"/>
+      <c r="S17" s="4"/>
+      <c r="T17" s="4"/>
+      <c r="U17" s="4"/>
+    </row>
+    <row r="18" customHeight="1" spans="14:21">
+      <c r="N18" s="4"/>
+      <c r="O18" s="4"/>
+      <c r="P18" s="4"/>
+      <c r="Q18" s="4"/>
+      <c r="R18" s="4"/>
+      <c r="S18" s="4"/>
+      <c r="T18" s="4"/>
+      <c r="U18" s="4"/>
+    </row>
+    <row r="20" customHeight="1" spans="3:8">
+      <c r="C20" s="4">
+        <v>13</v>
+      </c>
+      <c r="D20" s="4">
+        <v>3</v>
+      </c>
+      <c r="E20" s="4">
+        <v>1</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="3:8">
+      <c r="C21" s="4">
         <v>14</v>
       </c>
-    </row>
-    <row r="10" s="4" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C10" s="4">
-        <v>5</v>
-      </c>
-      <c r="D10" s="4">
-        <v>5</v>
-      </c>
-      <c r="E10" s="7" t="s">
+      <c r="D21" s="4">
+        <v>3</v>
+      </c>
+      <c r="E21" s="4">
+        <v>2</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="3:21">
+      <c r="C22" s="4">
+        <v>15</v>
+      </c>
+      <c r="D22" s="4">
+        <v>3</v>
+      </c>
+      <c r="E22" s="4">
+        <v>3</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="N22" s="4"/>
+      <c r="O22" s="4"/>
+      <c r="P22" s="4"/>
+      <c r="Q22" s="4"/>
+      <c r="R22" s="4"/>
+      <c r="S22" s="4"/>
+      <c r="T22" s="4"/>
+      <c r="U22" s="4"/>
+    </row>
+    <row r="23" customHeight="1" spans="3:21">
+      <c r="C23" s="4">
         <v>16</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="D23" s="4">
+        <v>3</v>
+      </c>
+      <c r="E23" s="4">
+        <v>4</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="N23" s="4"/>
+      <c r="O23" s="4"/>
+      <c r="P23" s="4"/>
+      <c r="Q23" s="4"/>
+      <c r="R23" s="4"/>
+      <c r="S23" s="4"/>
+      <c r="T23" s="4"/>
+      <c r="U23" s="4"/>
+    </row>
+    <row r="27" customHeight="1" spans="1:8">
+      <c r="A27" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G10" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" s="4" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C11" s="4">
-        <v>6</v>
-      </c>
-      <c r="D11" s="4">
-        <v>6</v>
-      </c>
-      <c r="E11" s="7" t="s">
+      <c r="B27" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" s="4">
         <v>19</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="D27" s="4">
+        <v>4</v>
+      </c>
+      <c r="E27" s="4">
+        <v>1</v>
+      </c>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+    </row>
+    <row r="28" customHeight="1" spans="1:8">
+      <c r="A28" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28" s="4">
         <v>20</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="D28" s="4">
+        <v>4</v>
+      </c>
+      <c r="E28" s="4">
+        <v>2</v>
+      </c>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+    </row>
+    <row r="29" customHeight="1" spans="1:8">
+      <c r="A29" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C29" s="4">
         <v>21</v>
       </c>
+      <c r="D29" s="4">
+        <v>4</v>
+      </c>
+      <c r="E29" s="4">
+        <v>3</v>
+      </c>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+    </row>
+    <row r="30" customHeight="1" spans="1:8">
+      <c r="A30" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C30" s="4">
+        <v>22</v>
+      </c>
+      <c r="D30" s="4">
+        <v>4</v>
+      </c>
+      <c r="E30" s="4">
+        <v>4</v>
+      </c>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+    </row>
+    <row r="31" customHeight="1" spans="6:8">
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+    </row>
+    <row r="32" customHeight="1" spans="6:8">
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3 E3 F3 G3 D4 E4 F4 G4 D5 E5 F5 G5 C3:C5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:H3 C4:H4 C5:H5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -1355,7 +1710,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:XFD19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2"/>
@@ -1369,120 +1724,120 @@
     <col min="13" max="16373" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:9">
+    <row r="1" s="1" customFormat="1" ht="13" spans="1:9">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:9">
+    <row r="2" s="1" customFormat="1" ht="13" spans="1:9">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:12">
+    <row r="3" s="1" customFormat="1" ht="13.5" spans="1:12">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="1:12">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="13.5" spans="1:12">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:12">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="13.5" spans="1:12">
       <c r="A5" s="2"/>
       <c r="B5" s="2" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="K5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>6</v>
-      </c>
       <c r="L5" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" customFormat="1" ht="27" customHeight="1" spans="3:12">
@@ -1490,7 +1845,7 @@
         <v>1000001</v>
       </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="E6">
         <v>15</v>
@@ -1502,10 +1857,10 @@
         <v>1</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J6">
         <v>5</v>
@@ -1522,7 +1877,7 @@
         <v>1000002</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="E7">
         <v>15</v>
@@ -1534,10 +1889,10 @@
         <v>1</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J7">
         <v>5</v>
@@ -1554,7 +1909,7 @@
         <v>1000003</v>
       </c>
       <c r="D8" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="E8">
         <v>15</v>
@@ -1566,10 +1921,10 @@
         <v>1</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J8">
         <v>5</v>
@@ -1586,7 +1941,7 @@
         <v>1000004</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="E9">
         <v>16</v>
@@ -1598,10 +1953,10 @@
         <v>1</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J9">
         <v>5</v>
@@ -1618,7 +1973,7 @@
         <v>1000005</v>
       </c>
       <c r="D10" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="E10">
         <v>16</v>
@@ -1630,10 +1985,10 @@
         <v>1</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J10">
         <v>5</v>
@@ -1650,7 +2005,7 @@
         <v>1000006</v>
       </c>
       <c r="D11" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="E11">
         <v>16</v>
@@ -1662,10 +2017,10 @@
         <v>1</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J11">
         <v>5</v>
@@ -1811,7 +2166,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3 E3 F3 G3 H3 I3 D4 E4 F4 G4 H4 I4 D5 E5 F5 G5 H5 I5 C3:C5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:I5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/ExclusiveAttrConfig.xlsx
+++ b/Excel/ExclusiveAttrConfig.xlsx
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="47">
   <si>
     <t>ID</t>
   </si>
@@ -140,22 +140,28 @@
     <t>5,10,20</t>
   </si>
   <si>
+    <t>5,10,15</t>
+  </si>
+  <si>
+    <t>10,20,40</t>
+  </si>
+  <si>
+    <t>2001,2002,2003,2010</t>
+  </si>
+  <si>
+    <t>20,40,80,20</t>
+  </si>
+  <si>
+    <t>5,10,15,5</t>
+  </si>
+  <si>
+    <t>40,80,160,40</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
     <t>0,0,0</t>
-  </si>
-  <si>
-    <t>10,20,40</t>
-  </si>
-  <si>
-    <t>2001,2002,2003,2010</t>
-  </si>
-  <si>
-    <t>20,40,80,20</t>
-  </si>
-  <si>
-    <t>0,0,0,0</t>
-  </si>
-  <si>
-    <t>40,80,160,40</t>
   </si>
   <si>
     <t>2001,2002,2003,2012</t>
@@ -1486,7 +1492,7 @@
         <v>31</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="14:21">
@@ -1526,7 +1532,7 @@
         <v>25</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:8">
@@ -1546,7 +1552,7 @@
         <v>27</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:21">
@@ -1560,13 +1566,13 @@
         <v>3</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G22" s="7" t="s">
         <v>29</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="N22" s="4"/>
       <c r="O22" s="4"/>
@@ -1588,13 +1594,13 @@
         <v>4</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G23" s="7" t="s">
         <v>31</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="N23" s="4"/>
       <c r="O23" s="4"/>
@@ -1697,7 +1703,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:H3 C4:H4 C5:H5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:H5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -1743,13 +1749,13 @@
         <v>0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>2</v>
@@ -1761,13 +1767,13 @@
         <v>4</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" ht="13.5" spans="1:12">
@@ -1777,13 +1783,13 @@
         <v>6</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>2</v>
@@ -1795,13 +1801,13 @@
         <v>4</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="13.5" spans="1:12">
@@ -1813,7 +1819,7 @@
         <v>7</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>7</v>
@@ -1845,7 +1851,7 @@
         <v>1000001</v>
       </c>
       <c r="D6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E6">
         <v>15</v>
@@ -1877,7 +1883,7 @@
         <v>1000002</v>
       </c>
       <c r="D7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E7">
         <v>15</v>
@@ -1909,7 +1915,7 @@
         <v>1000003</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E8">
         <v>15</v>
@@ -1941,7 +1947,7 @@
         <v>1000004</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E9">
         <v>16</v>
@@ -1973,7 +1979,7 @@
         <v>1000005</v>
       </c>
       <c r="D10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E10">
         <v>16</v>
@@ -2005,7 +2011,7 @@
         <v>1000006</v>
       </c>
       <c r="D11" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E11">
         <v>16</v>

--- a/Excel/ExclusiveAttrConfig.xlsx
+++ b/Excel/ExclusiveAttrConfig.xlsx
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="53">
   <si>
     <t>ID</t>
   </si>
@@ -161,10 +161,28 @@
     <t>0,0,0,0</t>
   </si>
   <si>
-    <t>0,0,0</t>
-  </si>
-  <si>
-    <t>2001,2002,2003,2012</t>
+    <t>2001,2012,2003</t>
+  </si>
+  <si>
+    <t>7,15,20</t>
+  </si>
+  <si>
+    <t>8,15,20</t>
+  </si>
+  <si>
+    <t>15,30,40</t>
+  </si>
+  <si>
+    <t>2001,2012,2003,2010</t>
+  </si>
+  <si>
+    <t>30,60,80,30</t>
+  </si>
+  <si>
+    <t>8,15,20,8</t>
+  </si>
+  <si>
+    <t>60,120,160,60</t>
   </si>
   <si>
     <t>Name</t>
@@ -392,12 +410,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1526,13 +1544,13 @@
         <v>1</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:8">
@@ -1546,13 +1564,13 @@
         <v>2</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:21">
@@ -1566,13 +1584,13 @@
         <v>3</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="N22" s="4"/>
       <c r="O22" s="4"/>
@@ -1594,10 +1612,10 @@
         <v>4</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="H23" s="7" t="s">
         <v>32</v>
@@ -1749,13 +1767,13 @@
         <v>0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>2</v>
@@ -1767,13 +1785,13 @@
         <v>4</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" ht="13.5" spans="1:12">
@@ -1783,13 +1801,13 @@
         <v>6</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>2</v>
@@ -1801,13 +1819,13 @@
         <v>4</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="13.5" spans="1:12">
@@ -1819,7 +1837,7 @@
         <v>7</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>7</v>
@@ -1851,7 +1869,7 @@
         <v>1000001</v>
       </c>
       <c r="D6" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E6">
         <v>15</v>
@@ -1883,7 +1901,7 @@
         <v>1000002</v>
       </c>
       <c r="D7" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E7">
         <v>15</v>
@@ -1915,7 +1933,7 @@
         <v>1000003</v>
       </c>
       <c r="D8" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E8">
         <v>15</v>
@@ -1947,7 +1965,7 @@
         <v>1000004</v>
       </c>
       <c r="D9" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E9">
         <v>16</v>
@@ -1979,7 +1997,7 @@
         <v>1000005</v>
       </c>
       <c r="D10" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E10">
         <v>16</v>
@@ -2011,7 +2029,7 @@
         <v>1000006</v>
       </c>
       <c r="D11" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E11">
         <v>16</v>

--- a/Excel/ExclusiveAttrConfig.xlsx
+++ b/Excel/ExclusiveAttrConfig.xlsx
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="60">
   <si>
     <t>ID</t>
   </si>
@@ -183,6 +183,27 @@
   </si>
   <si>
     <t>60,120,160,60</t>
+  </si>
+  <si>
+    <t>2001,2012,2003,2013</t>
+  </si>
+  <si>
+    <t>8,16,24,8</t>
+  </si>
+  <si>
+    <t>10,20,30,10</t>
+  </si>
+  <si>
+    <t>16,32,48,16</t>
+  </si>
+  <si>
+    <t>2001,2012,2003,2013,2010</t>
+  </si>
+  <si>
+    <t>32,64,96,32,32</t>
+  </si>
+  <si>
+    <t>10,20,30,10,10</t>
   </si>
   <si>
     <t>Name</t>
@@ -410,12 +431,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1221,21 +1242,21 @@
     <col min="16369" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="4" customFormat="1" customHeight="1" spans="1:8">
+    <row r="1" s="4" customFormat="1" customHeight="1" spans="1:21">
       <c r="A1" s="5"/>
       <c r="B1" s="5"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
     </row>
-    <row r="2" s="4" customFormat="1" customHeight="1" spans="1:8">
+    <row r="2" s="4" customFormat="1" customHeight="1" spans="1:21">
       <c r="A2" s="5"/>
       <c r="B2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
     </row>
-    <row r="3" s="4" customFormat="1" customHeight="1" spans="1:8">
+    <row r="3" s="4" customFormat="1" customHeight="1" spans="1:21">
       <c r="A3" s="5"/>
       <c r="B3" s="5"/>
       <c r="C3" s="6" t="s">
@@ -1257,7 +1278,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" s="4" customFormat="1" customHeight="1" spans="1:8">
+    <row r="4" s="4" customFormat="1" customHeight="1" spans="1:21">
       <c r="A4" s="5"/>
       <c r="B4" s="5"/>
       <c r="C4" s="6" t="s">
@@ -1279,7 +1300,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" s="4" customFormat="1" customHeight="1" spans="1:8">
+    <row r="5" s="4" customFormat="1" customHeight="1" spans="1:21">
       <c r="A5" s="5"/>
       <c r="B5" s="5"/>
       <c r="C5" s="6" t="s">
@@ -1301,7 +1322,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" s="4" customFormat="1" customHeight="1" spans="3:8">
+    <row r="6" s="4" customFormat="1" customHeight="1" spans="1:21">
       <c r="C6" s="4">
         <v>1</v>
       </c>
@@ -1321,7 +1342,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" s="4" customFormat="1" customHeight="1" spans="3:8">
+    <row r="7" s="4" customFormat="1" customHeight="1" spans="1:21">
       <c r="C7" s="4">
         <v>2</v>
       </c>
@@ -1341,7 +1362,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" s="4" customFormat="1" customHeight="1" spans="3:8">
+    <row r="8" s="4" customFormat="1" customHeight="1" spans="1:21">
       <c r="C8" s="4">
         <v>3</v>
       </c>
@@ -1361,7 +1382,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" s="4" customFormat="1" customHeight="1" spans="3:8">
+    <row r="9" s="4" customFormat="1" customHeight="1" spans="1:21">
       <c r="C9" s="4">
         <v>4</v>
       </c>
@@ -1381,7 +1402,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" s="4" customFormat="1" customHeight="1" spans="14:21">
+    <row r="10" s="4" customFormat="1" customHeight="1" spans="1:21">
       <c r="N10" s="4" t="s">
         <v>17</v>
       </c>
@@ -1407,7 +1428,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" s="4" customFormat="1" customHeight="1" spans="14:21">
+    <row r="11" s="4" customFormat="1" customHeight="1" spans="1:21">
       <c r="N11" s="4" t="s">
         <v>17</v>
       </c>
@@ -1433,7 +1454,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="3:8">
+    <row r="13" customHeight="1" spans="1:21">
       <c r="C13" s="4">
         <v>7</v>
       </c>
@@ -1453,7 +1474,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="3:8">
+    <row r="14" customHeight="1" spans="1:21">
       <c r="C14" s="4">
         <v>8</v>
       </c>
@@ -1473,7 +1494,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="3:8">
+    <row r="15" customHeight="1" spans="1:21">
       <c r="C15" s="4">
         <v>9</v>
       </c>
@@ -1493,7 +1514,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="3:8">
+    <row r="16" customHeight="1" spans="1:21">
       <c r="C16" s="4">
         <v>10</v>
       </c>
@@ -1513,7 +1534,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="14:21">
+    <row r="17" customHeight="1" spans="1:21">
       <c r="N17" s="4"/>
       <c r="O17" s="4"/>
       <c r="P17" s="4"/>
@@ -1523,7 +1544,7 @@
       <c r="T17" s="4"/>
       <c r="U17" s="4"/>
     </row>
-    <row r="18" customHeight="1" spans="14:21">
+    <row r="18" customHeight="1" spans="1:21">
       <c r="N18" s="4"/>
       <c r="O18" s="4"/>
       <c r="P18" s="4"/>
@@ -1533,7 +1554,7 @@
       <c r="T18" s="4"/>
       <c r="U18" s="4"/>
     </row>
-    <row r="20" customHeight="1" spans="3:8">
+    <row r="20" customHeight="1" spans="1:21">
       <c r="C20" s="4">
         <v>13</v>
       </c>
@@ -1553,7 +1574,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="21" customHeight="1" spans="3:8">
+    <row r="21" customHeight="1" spans="1:21">
       <c r="C21" s="4">
         <v>14</v>
       </c>
@@ -1573,7 +1594,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="22" customHeight="1" spans="3:21">
+    <row r="22" customHeight="1" spans="1:21">
       <c r="C22" s="4">
         <v>15</v>
       </c>
@@ -1601,7 +1622,7 @@
       <c r="T22" s="4"/>
       <c r="U22" s="4"/>
     </row>
-    <row r="23" customHeight="1" spans="3:21">
+    <row r="23" customHeight="1" spans="1:21">
       <c r="C23" s="4">
         <v>16</v>
       </c>
@@ -1629,13 +1650,7 @@
       <c r="T23" s="4"/>
       <c r="U23" s="4"/>
     </row>
-    <row r="27" customHeight="1" spans="1:8">
-      <c r="A27" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>17</v>
-      </c>
+    <row r="27" customHeight="1" spans="1:21">
       <c r="C27" s="4">
         <v>19</v>
       </c>
@@ -1645,17 +1660,17 @@
       <c r="E27" s="4">
         <v>1</v>
       </c>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4"/>
-    </row>
-    <row r="28" customHeight="1" spans="1:8">
-      <c r="A28" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>17</v>
-      </c>
+      <c r="F27" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="1:21">
       <c r="C28" s="4">
         <v>20</v>
       </c>
@@ -1665,17 +1680,17 @@
       <c r="E28" s="4">
         <v>2</v>
       </c>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
-    </row>
-    <row r="29" customHeight="1" spans="1:8">
-      <c r="A29" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>17</v>
-      </c>
+      <c r="F28" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="1:21">
       <c r="C29" s="4">
         <v>21</v>
       </c>
@@ -1685,11 +1700,17 @@
       <c r="E29" s="4">
         <v>3</v>
       </c>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="4"/>
-    </row>
-    <row r="30" customHeight="1" spans="1:8">
+      <c r="F29" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="1:21">
       <c r="A30" s="5" t="s">
         <v>17</v>
       </c>
@@ -1709,12 +1730,12 @@
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
     </row>
-    <row r="31" customHeight="1" spans="6:8">
+    <row r="31" customHeight="1" spans="1:21">
       <c r="F31" s="4"/>
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
     </row>
-    <row r="32" customHeight="1" spans="6:8">
+    <row r="32" customHeight="1" spans="1:21">
       <c r="F32" s="4"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
@@ -1748,32 +1769,32 @@
     <col min="13" max="16373" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="13" spans="1:9">
+    <row r="1" s="1" customFormat="1" ht="13" spans="1:12 16374:16384">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
     </row>
-    <row r="2" s="1" customFormat="1" ht="13" spans="1:9">
+    <row r="2" s="1" customFormat="1" ht="13" spans="1:12 16374:16384">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
     </row>
-    <row r="3" s="1" customFormat="1" ht="13.5" spans="1:12">
+    <row r="3" s="1" customFormat="1" ht="13.5" spans="1:12 16374:16384">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>2</v>
@@ -1785,29 +1806,29 @@
         <v>4</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" ht="13.5" spans="1:12">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="13.5" spans="1:12 16374:16384">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>2</v>
@@ -1819,16 +1840,16 @@
         <v>4</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" ht="13.5" spans="1:12">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="13.5" spans="1:12 16374:16384">
       <c r="A5" s="2"/>
       <c r="B5" s="2" t="s">
         <v>17</v>
@@ -1837,7 +1858,7 @@
         <v>7</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>7</v>
@@ -1864,12 +1885,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" customFormat="1" ht="27" customHeight="1" spans="3:12">
+    <row r="6" customFormat="1" ht="27" customHeight="1" spans="1:12 16374:16384">
       <c r="C6">
         <v>1000001</v>
       </c>
       <c r="D6" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="E6">
         <v>15</v>
@@ -1896,12 +1917,12 @@
         <v>10010</v>
       </c>
     </row>
-    <row r="7" customFormat="1" ht="27" customHeight="1" spans="3:12">
+    <row r="7" customFormat="1" ht="27" customHeight="1" spans="1:12 16374:16384">
       <c r="C7">
         <v>1000002</v>
       </c>
       <c r="D7" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="E7">
         <v>15</v>
@@ -1928,12 +1949,12 @@
         <v>10024</v>
       </c>
     </row>
-    <row r="8" customFormat="1" ht="27" customHeight="1" spans="3:12">
+    <row r="8" customFormat="1" ht="27" customHeight="1" spans="1:12 16374:16384">
       <c r="C8">
         <v>1000003</v>
       </c>
       <c r="D8" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="E8">
         <v>15</v>
@@ -1960,12 +1981,12 @@
         <v>10038</v>
       </c>
     </row>
-    <row r="9" customFormat="1" ht="27" customHeight="1" spans="3:12">
+    <row r="9" customFormat="1" ht="27" customHeight="1" spans="1:12 16374:16384">
       <c r="C9">
         <v>1000004</v>
       </c>
       <c r="D9" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="E9">
         <v>16</v>
@@ -1992,12 +2013,12 @@
         <v>10010</v>
       </c>
     </row>
-    <row r="10" customFormat="1" ht="27" customHeight="1" spans="3:12">
+    <row r="10" customFormat="1" ht="27" customHeight="1" spans="1:12 16374:16384">
       <c r="C10">
         <v>1000005</v>
       </c>
       <c r="D10" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="E10">
         <v>16</v>
@@ -2024,12 +2045,12 @@
         <v>10024</v>
       </c>
     </row>
-    <row r="11" customFormat="1" ht="27" customHeight="1" spans="3:12">
+    <row r="11" customFormat="1" ht="27" customHeight="1" spans="1:12 16374:16384">
       <c r="C11">
         <v>1000006</v>
       </c>
       <c r="D11" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="E11">
         <v>16</v>
@@ -2056,13 +2077,13 @@
         <v>10038</v>
       </c>
     </row>
-    <row r="12" customFormat="1" ht="27" customHeight="1" spans="6:6">
+    <row r="12" customFormat="1" ht="27" customHeight="1" spans="1:12 16374:16384">
       <c r="F12" s="1"/>
     </row>
-    <row r="13" customFormat="1" ht="27" customHeight="1" spans="6:6">
+    <row r="13" customFormat="1" ht="27" customHeight="1" spans="1:12 16374:16384">
       <c r="F13" s="1"/>
     </row>
-    <row r="14" s="2" customFormat="1" spans="3:16384">
+    <row r="14" s="2" customFormat="1" spans="1:12 16374:16384">
       <c r="C14"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
@@ -2083,7 +2104,7 @@
       <c r="XFC14"/>
       <c r="XFD14"/>
     </row>
-    <row r="15" s="2" customFormat="1" spans="3:16384">
+    <row r="15" s="2" customFormat="1" spans="1:12 16374:16384">
       <c r="C15"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
@@ -2104,7 +2125,7 @@
       <c r="XFC15"/>
       <c r="XFD15"/>
     </row>
-    <row r="16" s="2" customFormat="1" spans="3:16384">
+    <row r="16" s="2" customFormat="1" spans="1:12 16374:16384">
       <c r="C16"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
@@ -2125,7 +2146,7 @@
       <c r="XFC16"/>
       <c r="XFD16"/>
     </row>
-    <row r="17" s="2" customFormat="1" spans="3:16384">
+    <row r="17" s="2" customFormat="1" spans="3:12 16374:16384">
       <c r="C17"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
@@ -2146,7 +2167,7 @@
       <c r="XFC17"/>
       <c r="XFD17"/>
     </row>
-    <row r="18" s="2" customFormat="1" spans="3:16384">
+    <row r="18" s="2" customFormat="1" spans="3:12 16374:16384">
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
@@ -2167,7 +2188,7 @@
       <c r="XFC18"/>
       <c r="XFD18"/>
     </row>
-    <row r="19" s="2" customFormat="1" spans="3:16384">
+    <row r="19" s="2" customFormat="1" spans="3:12 16374:16384">
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
